--- a/תפקידים-וסיכויים.xlsx
+++ b/תפקידים-וסיכויים.xlsx
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>0.581</v>
+        <v>0.579</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>0.043</v>
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.555</v>
+        <v>0.5539999999999999</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>0.027</v>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.512</v>
+        <v>0.51</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0.026</v>
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>0.215</v>
+        <v>0.214</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>0.057</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G7" s="11" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.141</v>
+        <v>0.14</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0.042</v>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.288</v>
+        <v>0.284</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.288</v>
+        <v>0.284</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G9" s="11" t="n">
         <v>0.679</v>
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.075</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>0.8420000000000001</v>
@@ -1348,7 +1348,7 @@
         <v>0.04</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>0.195</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.038</v>
       </c>
       <c r="E15" s="11" t="n">
         <v>0.022</v>
@@ -1480,7 +1480,7 @@
         <v>0.033</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>0.7929999999999999</v>
@@ -1610,7 +1610,7 @@
         <v>0.027</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>0.797</v>
@@ -1804,13 +1804,13 @@
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.022</v>
+        <v>0.025</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.019</v>
+        <v>0.023</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="G21" s="11" t="n">
         <v>0.399</v>
@@ -2140,7 +2140,7 @@
         <v>0.042</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>0.51</v>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
       <c r="E29" s="11" t="n">
         <v>0.017</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="G29" s="11" t="n">
         <v>0</v>
@@ -2394,7 +2394,7 @@
     <row r="30" ht="96" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>תקשוב ותמיכה טכנית</t>
+          <t>בינוי, תחזוקה ותשתיות</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -2414,18 +2414,86 @@
         <v>0.005</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="G30" s="7" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>תכנון ותחזוקת המבנים והתשתיות — הנדסה בשירות הארגון.
+היום-יום: עבודה הנדסית: ליווי פרויקטים בשטח, פיקוח על קבלנים, ניהול תקציב ותכנון תחזוקה.</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>• הנדסה / אדריכלות  (+3)  ← באיזה תחום התואר / הלימודים שלך?
+• משרד  (+3)  ← איזו סביבת עבודה מדברת אליך?
+• מול עובדים אחרים בארגון  (+3)  ← מול מי היית רוצה לעבוד?
+• ציוד, מלאי ותשתיות  (+3)  ← עם מה מתחשק לך לעבוד ביום-יום?
+• "הכול עבד חלק כי דאגתי שיהיה"  (+3)  ← מה ייתן לך הכי הרבה סיפוק בסוף יום עבודה?
+• מעדיף/ה תפקיד ללא דרישה גופנית  (+2)  ← מה רמת הכושר הגופני והנכונות למאמץ פיזי?</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>רקע אקדמי ב: הנדסה / אדריכלות</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>• מהנדס/ת או הנדסאי/ת בניין / אדריכלות
+• ניסיון בניהול פרויקטים בבינוי ו/או תחזוקת מבנים
+• ניסיון בניהול תקציבים ובמשא ומתן מול קבלנים וספקים
+• רישיון נהיגה</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>נמסר ביום המיון</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>דף התפקידים הרשמי</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="96" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>תקשוב ותמיכה טכנית</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>מנהלה</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>מנהלה מקצועית</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G31" s="11" t="n">
         <v>0.894</v>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>התשתית הטכנולוגית בשטח — קשר, רשת ותמיכה ליחידות.
 היום-יום: עבודה טכנית ביחידות: התקנות, טיפול בתקלות, תמיכה למשתמשים והדרכות.</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="I31" s="12" t="inlineStr">
         <is>
           <t>• מערכות טכנולוגיות וציוד תקשורת  (+4)  ← עם מה מתחשק לך לעבוד ביום-יום?
 • משרד  (+3)  ← איזו סביבת עבודה מדברת אליך?
@@ -2435,12 +2503,12 @@
 • מעדיף/ה תפקיד ללא דרישה גופנית  (+2)  ← מה רמת הכושר הגופני והנכונות למאמץ פיזי?</t>
         </is>
       </c>
-      <c r="J30" s="8" t="inlineStr">
+      <c r="J31" s="12" t="inlineStr">
         <is>
           <t>רקע אקדמי ב: מדעי המחשב / סייבר / הנדסה / אדריכלות</t>
         </is>
       </c>
-      <c r="K30" s="8" t="inlineStr">
+      <c r="K31" s="12" t="inlineStr">
         <is>
           <t>• מהנדס/טכנאי/הנדסאי חשמל, אלקטרוניקה או מחשבים
 • ניסיון בתחום החומרה, התוכנה, האלקטרוניקה והרשת
@@ -2448,52 +2516,52 @@
 • רישיון נהיגה</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr">
+      <c r="L31" s="12" t="inlineStr">
         <is>
           <t>נמסר ביום המיון</t>
         </is>
       </c>
-      <c r="M30" s="6" t="inlineStr">
+      <c r="M31" s="10" t="inlineStr">
         <is>
           <t>דף התפקידים הרשמי</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="96" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="32" ht="96" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>שכר, גמלאות וכספים</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>מנהלה</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>מנהלה מקצועית</t>
         </is>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D32" s="7" t="n">
         <v>0.005</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E32" s="7" t="n">
         <v>0.004</v>
       </c>
-      <c r="F31" s="11" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="G31" s="11" t="n">
+      <c r="F32" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G32" s="7" t="n">
         <v>0.9540000000000001</v>
       </c>
-      <c r="H31" s="12" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>חישוב שכר, גמלאות ותקציב — עבודה מדויקת מול מספרים ונהלים.
 היום-יום: עבודה מדויקת מול מערכות שכר ותקציב: קליטת נתונים, בקרות, יישום הסכמים וטיפול בפניות פרטניות.</t>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>• מספרים, תקציבים וחוזים  (+4)  ← עם מה מתחשק לך לעבוד ביום-יום?
 • כלכלה / מנהל עסקים / ראיית חשבון  (+3)  ← באיזה תחום התואר / הלימודים שלך?
@@ -2503,12 +2571,12 @@
 • ניתוח, מספרים ופתרון בעיות  (+3)  ← מה הכי חשוב לך בעבודה?</t>
         </is>
       </c>
-      <c r="J31" s="12" t="inlineStr">
+      <c r="J32" s="8" t="inlineStr">
         <is>
           <t>רקע אקדמי ב: כלכלה / מנהל עסקים / ראיית חשבון</t>
         </is>
       </c>
-      <c r="K31" s="12" t="inlineStr">
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>• תעודת קורס חשבי שכר בכיר / הנהלת חשבונות
 • תואר אקדמי בכלכלה ו/או מנהל עסקים
@@ -2516,120 +2584,185 @@
 • שליטה ביישומי מחשב ובמערכות שכר</t>
         </is>
       </c>
-      <c r="L31" s="12" t="inlineStr">
+      <c r="L32" s="8" t="inlineStr">
         <is>
           <t>נמסר ביום המיון</t>
         </is>
       </c>
-      <c r="M31" s="10" t="inlineStr">
+      <c r="M32" s="6" t="inlineStr">
         <is>
           <t>דף התפקידים הרשמי</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="96" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>בינוי, תחזוקה ותשתיות</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
+    <row r="33" ht="96" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>סטודנט/ית — עוזר/ת לעובד/ת סוציאלי/ת</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>מנהלה</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>מנהלה מקצועית</t>
         </is>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D33" s="11" t="n">
         <v>0.005</v>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="E33" s="11" t="n">
         <v>0.004</v>
       </c>
-      <c r="F32" s="7" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>תכנון ותחזוקת המבנים והתשתיות — הנדסה בשירות הארגון.
-היום-יום: עבודה הנדסית: ליווי פרויקטים בשטח, פיקוח על קבלנים, ניהול תקציב ותכנון תחזוקה.</t>
-        </is>
-      </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>• הנדסה / אדריכלות  (+3)  ← באיזה תחום התואר / הלימודים שלך?
+      <c r="F33" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>מסלול סטודנטים בתחום הרווחה — סיוע לעובד/ת סוציאלי/ת בארגון.
+היום-יום: משמרות מותאמות ללימודים: סיוע בפניות ובליווי, עבודה מול גורמי רווחה בארגון ותיעוד מקצועי.</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>• בריאות / עבודה סוציאלית  (+3)  ← באיזה תחום התואר / הלימודים שלך?
+• סטודנט/ית פעיל/ה (או מתחיל/ה תוך שנה)  (+2)  ← מה המצב שלך כרגע?
+• מול עובדים אחרים בארגון  (+2)  ← מול מי היית רוצה לעבוד?
+• לעזור לאנשים ולהשפיע על חייהם  (+2)  ← מה הכי חשוב לך בעבודה?
+• "עזרתי למישהו שהיה צריך אותי"  (+2)  ← מה ייתן לך הכי הרבה סיפוק בסוף יום עבודה?
+• שילוב עם לימודים (סטודנט)  (+2)  ← מה תפיסת הקריירה שלך?</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>סטודנט/ית · יתרת לימודים של שנה לפחות · רקע אקדמי ב: בריאות / עבודה סוציאלית / מדעי החברה</t>
+        </is>
+      </c>
+      <c r="K33" s="12" t="inlineStr">
+        <is>
+          <t>• לימודים בתחום עבודה סוציאלית / בריאות / מדעי החברה
+• יתרת לימודים של שנה לפחות</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>נמסר ביום המיון</t>
+        </is>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>דף התפקידים הרשמי</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="96" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>משפט ותביעה</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>מנהלה</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>מנהלה מקצועית</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>0.9740000000000001</v>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>הכנת כתבי אישום וייצוג בבתי משפט — הזרוע המשפטית של האכיפה.
+היום-יום: עבודה משפטית: הכנת תיקים וכתבי אישום, כתיבת חוות דעת והופעה בבית משפט.</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>• טקסטים, מסמכים ונהלים  (+4)  ← עם מה מתחשק לך לעבוד ביום-יום?
+• משפטים  (+3)  ← באיזה תחום התואר / הלימודים שלך?
 • משרד  (+3)  ← איזו סביבת עבודה מדברת אליך?
 • מול עובדים אחרים בארגון  (+3)  ← מול מי היית רוצה לעבוד?
-• ציוד, מלאי ותשתיות  (+3)  ← עם מה מתחשק לך לעבוד ביום-יום?
-• "הכול עבד חלק כי דאגתי שיהיה"  (+3)  ← מה ייתן לך הכי הרבה סיפוק בסוף יום עבודה?
-• מעדיף/ה תפקיד ללא דרישה גופנית  (+2)  ← מה רמת הכושר הגופני והנכונות למאמץ פיזי?</t>
-        </is>
-      </c>
-      <c r="J32" s="8" t="inlineStr">
-        <is>
-          <t>רקע אקדמי ב: הנדסה / אדריכלות</t>
-        </is>
-      </c>
-      <c r="K32" s="8" t="inlineStr">
-        <is>
-          <t>• מהנדס/ת או הנדסאי/ת בניין / אדריכלות
-• ניסיון בניהול פרויקטים בבינוי ו/או תחזוקת מבנים
-• ניסיון בניהול תקציבים ובמשא ומתן מול קבלנים וספקים
-• רישיון נהיגה</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
+• מעדיף/ה תפקיד ללא דרישה גופנית  (+2)  ← מה רמת הכושר הגופני והנכונות למאמץ פיזי?
+• מעדיף/ה בוקר/צהריים קבוע  (+2)  ← מה היחס שלך למשמרות ולעבודת לילה?</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>תואר אקדמי · רקע אקדמי ב: משפטים</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>• תואר ראשון במשפטים ורישיון בעריכת דין
+• ניסיון בייצוג משפטי בבתי משפט
+• ניסיון במשפט פלילי</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
         <is>
           <t>נמסר ביום המיון</t>
         </is>
       </c>
-      <c r="M32" s="6" t="inlineStr">
+      <c r="M34" s="6" t="inlineStr">
         <is>
           <t>דף התפקידים הרשמי</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="96" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="35" ht="96" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>רווחה ועבודה סוציאלית</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>מנהלה</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>מנהלה מקצועית</t>
         </is>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D35" s="11" t="n">
         <v>0.003</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E35" s="11" t="n">
         <v>0.002</v>
       </c>
-      <c r="F33" s="11" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G33" s="11" t="n">
+      <c r="F35" s="11" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G35" s="11" t="n">
         <v>0.972</v>
       </c>
-      <c r="H33" s="12" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>טיפול רווחתי בשוטרים ובמשפחותיהם — מיצוי זכויות, ליווי נפגעים ומשפחות שכולות.
 היום-יום: עבודה מול שוטרים ומשפחות: פניות אישיות, ליווי ומיצוי זכויות, תיאום מול גורמי סיוע וטיפול באירועי רווחה.</t>
         </is>
       </c>
-      <c r="I33" s="12" t="inlineStr">
+      <c r="I35" s="12" t="inlineStr">
         <is>
           <t>• לעזור לאנשים ולהשפיע על חייהם  (+4)  ← מה הכי חשוב לך בעבודה?
 • בריאות / עבודה סוציאלית  (+3)  ← באיזה תחום התואר / הלימודים שלך?
@@ -2639,151 +2772,18 @@
 • "עזרתי למישהו שהיה צריך אותי"  (+3)  ← מה ייתן לך הכי הרבה סיפוק בסוף יום עבודה?</t>
         </is>
       </c>
-      <c r="J33" s="12" t="inlineStr">
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>תואר אקדמי · רקע אקדמי ב: בריאות / עבודה סוציאלית</t>
         </is>
       </c>
-      <c r="K33" s="12" t="inlineStr">
+      <c r="K35" s="12" t="inlineStr">
         <is>
           <t>• תואר ראשון בעבודה סוציאלית
 • ניסיון בתחום עבודת רווחה ו/או בחקירות נוער, חסרי ישע ונפגעי עבירה
 • לתפקידי בריאות הנפש — ניסיון בעבודה קלינית</t>
         </is>
       </c>
-      <c r="L33" s="12" t="inlineStr">
-        <is>
-          <t>נמסר ביום המיון</t>
-        </is>
-      </c>
-      <c r="M33" s="10" t="inlineStr">
-        <is>
-          <t>דף התפקידים הרשמי</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="96" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>משפט ותביעה</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>מנהלה</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>מנהלה מקצועית</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>0.9740000000000001</v>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>הכנת כתבי אישום וייצוג בבתי משפט — הזרוע המשפטית של האכיפה.
-היום-יום: עבודה משפטית: הכנת תיקים וכתבי אישום, כתיבת חוות דעת והופעה בבית משפט.</t>
-        </is>
-      </c>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t>• טקסטים, מסמכים ונהלים  (+4)  ← עם מה מתחשק לך לעבוד ביום-יום?
-• משפטים  (+3)  ← באיזה תחום התואר / הלימודים שלך?
-• משרד  (+3)  ← איזו סביבת עבודה מדברת אליך?
-• מול עובדים אחרים בארגון  (+3)  ← מול מי היית רוצה לעבוד?
-• מעדיף/ה תפקיד ללא דרישה גופנית  (+2)  ← מה רמת הכושר הגופני והנכונות למאמץ פיזי?
-• מעדיף/ה בוקר/צהריים קבוע  (+2)  ← מה היחס שלך למשמרות ולעבודת לילה?</t>
-        </is>
-      </c>
-      <c r="J34" s="8" t="inlineStr">
-        <is>
-          <t>תואר אקדמי · רקע אקדמי ב: משפטים</t>
-        </is>
-      </c>
-      <c r="K34" s="8" t="inlineStr">
-        <is>
-          <t>• תואר ראשון במשפטים ורישיון בעריכת דין
-• ניסיון בייצוג משפטי בבתי משפט
-• ניסיון במשפט פלילי</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
-        <is>
-          <t>נמסר ביום המיון</t>
-        </is>
-      </c>
-      <c r="M34" s="6" t="inlineStr">
-        <is>
-          <t>דף התפקידים הרשמי</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="96" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>סטודנט/ית — עוזר/ת לעובד/ת סוציאלי/ת</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>מנהלה</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>מנהלה מקצועית</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="E35" s="11" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="F35" s="11" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="G35" s="11" t="n">
-        <v>0.968</v>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>מסלול סטודנטים בתחום הרווחה — סיוע לעובד/ת סוציאלי/ת בארגון.
-היום-יום: משמרות מותאמות ללימודים: סיוע בפניות ובליווי, עבודה מול גורמי רווחה בארגון ותיעוד מקצועי.</t>
-        </is>
-      </c>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>• בריאות / עבודה סוציאלית  (+3)  ← באיזה תחום התואר / הלימודים שלך?
-• סטודנט/ית פעיל/ה (או מתחיל/ה תוך שנה)  (+2)  ← מה המצב שלך כרגע?
-• מול עובדים אחרים בארגון  (+2)  ← מול מי היית רוצה לעבוד?
-• לעזור לאנשים ולהשפיע על חייהם  (+2)  ← מה הכי חשוב לך בעבודה?
-• "עזרתי למישהו שהיה צריך אותי"  (+2)  ← מה ייתן לך הכי הרבה סיפוק בסוף יום עבודה?
-• שילוב עם לימודים (סטודנט)  (+2)  ← מה תפיסת הקריירה שלך?</t>
-        </is>
-      </c>
-      <c r="J35" s="12" t="inlineStr">
-        <is>
-          <t>סטודנט/ית · יתרת לימודים של שנה לפחות · רקע אקדמי ב: בריאות / עבודה סוציאלית / מדעי החברה</t>
-        </is>
-      </c>
-      <c r="K35" s="12" t="inlineStr">
-        <is>
-          <t>• לימודים בתחום עבודה סוציאלית / בריאות / מדעי החברה
-• יתרת לימודים של שנה לפחות</t>
-        </is>
-      </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
           <t>נמסר ביום המיון</t>
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.55</v>
+        <v>0.71</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>0.953</v>
